--- a/data/database_status.xlsx
+++ b/data/database_status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uqlngo2\Documents\GitHub\RIFR_Map\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C193A92-503E-4820-9077-2AE053C71FF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB140CD1-32E8-4796-8FE6-19D69FA99EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-1485" windowWidth="29040" windowHeight="15720" xr2:uid="{9BBD2626-AADE-4B89-8BD3-2FC849FF55ED}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="19420" windowHeight="11500" xr2:uid="{9BBD2626-AADE-4B89-8BD3-2FC849FF55ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>Database</t>
   </si>
@@ -57,6 +57,66 @@
   </si>
   <si>
     <t>The Comprehensive Antibiotic Resistance Database (CARD)</t>
+  </si>
+  <si>
+    <t>TBDReaMDB</t>
+  </si>
+  <si>
+    <t>This site can't be reached</t>
+  </si>
+  <si>
+    <t>MUBII-TB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Page not found </t>
+  </si>
+  <si>
+    <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4021062/</t>
+  </si>
+  <si>
+    <t>https://journals.plos.org/plosmedicine/article?id=10.1371/journal.pmed.1000002</t>
+  </si>
+  <si>
+    <t>https://academic.oup.com/nar/article/37/suppl_1/D443/1002454</t>
+  </si>
+  <si>
+    <t>CRyPTIC</t>
+  </si>
+  <si>
+    <t>DRAGdb</t>
+  </si>
+  <si>
+    <t>AMRFinderPlus</t>
+  </si>
+  <si>
+    <t>ResFinder </t>
+  </si>
+  <si>
+    <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8914360/</t>
+  </si>
+  <si>
+    <t>https://www.nature.com/articles/s41598-020-65766-8</t>
+  </si>
+  <si>
+    <t>Website</t>
+  </si>
+  <si>
+    <t>https://bicresources.jcbose.ac.in/ssaha4/drag/</t>
+  </si>
+  <si>
+    <t>https://card.mcmaster.ca/</t>
+  </si>
+  <si>
+    <t>https://journals.plos.org/plosbiology/article?id=10.1371/journal.pbio.3001721</t>
+  </si>
+  <si>
+    <t>No website</t>
+  </si>
+  <si>
+    <t>Paper/Document</t>
+  </si>
+  <si>
+    <t>https://www.nature.com/articles/s41598-021-91456-0</t>
   </si>
 </sst>
 </file>
@@ -428,14 +488,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EABEBCF3-8632-4D7F-A7B9-07630C6D851C}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="51.36328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="24.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -443,10 +504,16 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -454,15 +521,82 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
+        <v>18</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/database_status.xlsx
+++ b/data/database_status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uqlngo2\Documents\GitHub\RIFR_Map\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB140CD1-32E8-4796-8FE6-19D69FA99EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3682C51F-D5F8-4C68-9B99-A797638EE788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="19420" windowHeight="11500" xr2:uid="{9BBD2626-AADE-4B89-8BD3-2FC849FF55ED}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{9BBD2626-AADE-4B89-8BD3-2FC849FF55ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
   <si>
     <t>Database</t>
   </si>
@@ -117,6 +117,9 @@
   </si>
   <si>
     <t>https://www.nature.com/articles/s41598-021-91456-0</t>
+  </si>
+  <si>
+    <t>PointFinder</t>
   </si>
 </sst>
 </file>
@@ -488,7 +491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EABEBCF3-8632-4D7F-A7B9-07630C6D851C}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="51.36328125" bestFit="1" customWidth="1"/>
@@ -595,6 +598,14 @@
         <v>18</v>
       </c>
     </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
